--- a/data-vh/2_квартал_2026_ВХ.xlsx
+++ b/data-vh/2_квартал_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$73</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,4975 +562,5267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q73"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="22.95" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000051</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001356 от 01.04.2026 15:04:13</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>ГК Демидов ООО (ЭДО Такском ЗП)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>_уу_Труба 89*3,5 ГОСТ 10704-91/ Ст3сп, Ст3сп5, В-Ст3сп (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>2.1.1.2.1.6 Трубы стальные электросварные прямошовные ГОСТ 10704-91</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="12" t="n">
         <v>2215</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="12" t="n">
         <v>2215</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Заусенец в виде гребня</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Заусенцы по торцу.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Взять в работу с доработкой</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="22.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000052</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001365 от 02.04.2026 12:07:22</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>ИНТЕРМЕТГРУПП ООО (ЭДО Такском ЗП)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>_уу_Г/к уголок 63*63*5,0 ГОСТ 8509-93/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>Уголок горячекатаный равнополочный ГОСТ 8509-93</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Отклонение от прямого угла допускается не более 2мм, фактически 10мм.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>В лом</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="22.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000053</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001355 от 01.04.2026 14:44:20</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>ГК Демидов ООО (ЭДО Такском ЗП)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>_уу_Труба 57*3,5 ГОСТ 10704-91/ Ст3сп, Ст3сп5, В-Ст3сп (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>2.1.1.2.1.6 Трубы стальные электросварные прямошовные ГОСТ 10704-91</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="12" t="n">
         <v>2052</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="12" t="n">
         <v>2052</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Заусенец в виде гребня</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Заусенецы по торцу</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>Взять в работу в штатном режиме.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="22.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000054</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001405 от 06.04.2026 10:14:57</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Сталепромышленная компания АО (инн 6671197148)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>_уу_Лист 2,5 ГОСТ 19903-2015/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Листы сталь Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Подгиб</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Прокат имеет загнутые уголки под углом более 90 градусов. Отклонение от плоскостности.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>Взять в работу в штатном режиме</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="22.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000055</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>08.04.2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001365 от 02.04.2026 12:07:22</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>ИНТЕРМЕТГРУПП ООО (ЭДО Такском ЗП)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Склад ПРОФИЛЬНЫЙ ПРОКАТ</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>_уу_Г/к уголок 75*75*6,0 ГОСТ 8509-93/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>Уголок горячекатаный равнополочный ГОСТ 8509-93</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>Отклонение от прямого угла допускается не более 2мм, фактически 5-7мм.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>В работу с доработкой</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="34.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000056</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>10.04.2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-000734 от 09.02.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>БАУТЕКС ООО (ЭДО Такском ПМ с 19.11.24; ЗП от 01.09.2025)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>_Склад корпус №9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Корпус световозвращателя КД-5 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>1.1.8.2 Световозвращатель КД5-КБII-R1</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>282</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="9" t="n">
         <v>36.66</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>В местах контакта с выталкивателями в наличии дефекты: облой на сопрягаемых поверхностях, сколы. Не обеспечена чёткая маркировка года выпуска и знака ЕАС. Трещины, раковины, бугорки, сухое место, сколы, сквозные отверстия.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>В лом</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" ht="46.95" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>В00-0000057</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>14.04.2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001479 от 09.04.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>СЕВЕРСТАЛЬ ДИСТРИБУЦИЯ АО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>_уу_Проволока 5,0-Ч-П-I ГОСТ 3282-74</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Проволока </t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="12" t="n">
         <v>19726</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="12" t="n">
         <v>19726</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>Номер плавки в сертификате качества №628061264 не соответствует номерам плавок, указанных в маркировочных бирках на поставленных мотках. В сертификате плавка 741559, на маркировочных бирках плавка 741525 и плавка 741565.</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>Сертификат поставщик заменил на корректный</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" ht="22.95" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>В00-0000058</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>17.04.2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001563 от 17.04.2026 10:25:34</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>ИНТЕРМЕТГРУПП ООО (ЭДО Такском ЗП)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>_уу_Лист 2,5 ГОСТ 19903-2015/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>Листы сталь Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>Подгиб</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>Прокат имеет загнутый уголок под углом более 90 градусов. Отклонение от плоскостности.</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>В работу с доработкой</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" ht="34.95" customHeight="1">
+      <c r="A10" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>В00-0000059</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>17.04.2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001327 от 21.03.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>ТУЛА-СТАЛЬ ТД ООО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>_уу_Г/к швеллер 12П ГОСТ 8240-97/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>2.1.1.2.2.1 Швеллер горячекатаный ГОСТ 8240-97</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="12" t="n">
         <v>15178</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="12" t="n">
         <v>15178</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>Согласно НТД содержание кремния 0,15-0,30%, фактически 0,12-0,13%</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>Повторный прожиг подтвердил соответствующее содержание кремния. Процессы по акту прекращены.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" ht="82.05" customHeight="1">
+      <c r="A11" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>В00-0000060</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>20.04.2026</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>БАУТЕКС ООО (ЭДО Такском ПМ с 19.11.24; ЗП от 01.09.2025)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>БАУТЕКС ООО (ЭДО Такском ПМ с 19.11.24; ЗП от 01.09.2025)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Корпус световозвращателя КД-5 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>1.1.8.2 Световозвращатель КД5-КБII-R1</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.65</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>По КД размер 105(-1)мм, фактически у изделия №3 101,7мм. По КД размер 113,3 (+-0,435)мм, фактически 111,5-112,1мм. По КД квадратное отверстие 18 (+0,43)мм, фактически 18,8*19мм. По КД расстояние от края отверстия до знака EAC 3,5 (+-0,15)мм, фактически 3мм. По КД расстояние от края отверстия до логотипа  2,5(+-0,125)мм фактически 2мм. По КД угол 40 градусов, фактически 45 градусов.На поверхности из0делия №3  механические дефекты. На поверхности изделия №5 раковины.</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="Q11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="22.95" customHeight="1">
+      <c r="A12" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>В00-0000061</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>22.04.2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001610 от 22.04.2026 12:38:16</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>ГК Демидов ООО (ЭДО Такском ЗП)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>_уу_Труба 32*3,2 ГОСТ 3262-75/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>2.1.1.2.1.8 Трубы стальные водогазопроводные ГОСТ 3262-75</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>Согласно НТД содержание кремния 0,15-0,30%, фактически 0,03-0,04%.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>Возвращено поставщику</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" ht="22.95" customHeight="1">
+      <c r="A13" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>В00-0000062</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>06.05.2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001791 от 06.05.2026 14:48:21</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>ТЗ ООО (6320041310)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Переходник МФГ30-М 001.51.00.001  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>Невыполнение технических требований КД</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>Отсутствует притупление острых кромок радиусом 0,5 мм. (МФГ30-М 001.51.00.001 п.3)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены поставщиком.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" ht="10.95" customHeight="1">
+      <c r="A14" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Секция основная Э 662.00.15.000, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="9" t="n">
         <v>1.36</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" ht="10.95" customHeight="1">
+      <c r="A15" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Секция балки Э 662.00.00.001, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="9" t="n">
         <v>4.48</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" ht="10.95" customHeight="1">
+      <c r="A16" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Шайба Э 662.00.00.002, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="11" t="n">
         <v>0.116</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" ht="10.95" customHeight="1">
+      <c r="A17" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Пластина Э 662.00.00.003, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" ht="10.95" customHeight="1">
+      <c r="A18" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Секция деформационная №2, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="9" t="n">
         <v>1.76</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" ht="22.95" customHeight="1">
+      <c r="A19" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Основание ФО-У-80 (Э 662.00.06.000), Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="9" t="n">
         <v>4.26</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" ht="10.95" customHeight="1">
+      <c r="A20" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Секция деформационная №8, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="9" t="n">
         <v>2.24</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" ht="10.95" customHeight="1">
+      <c r="A21" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>В00-0000063</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>ИП Бекетов В.С.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>ОО_ГПЦ(30) Плита начальная Э 662.00.12.001, Оцинкованное, (опытный образец)</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>НА ВЫСТАВКУ</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="9" t="n">
         <v>0.34</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Неустранимое</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>1.  Цинковое покрытие не соответствует требованиям КД</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" ht="22.95" customHeight="1">
+      <c r="A22" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>В00-0000064</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000198 от 13.05.2026 13:53:20</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х445х545) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="9" t="n">
         <v>108.34</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>500±20 факт. 40,30 – 40,90;    500±20 факт. 38,60 – 39,70;    5±0,2 факт. 4,2-5,0.    Заусенцы.</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>Доработано подрядчиком</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" ht="22.95" customHeight="1">
+      <c r="A23" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>В00-0000064</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000198 от 13.05.2026 13:53:20</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х454х470) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="9" t="n">
         <v>47.22</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>55±0,4 факт. 63;    500±20 факт. 400;    5±0,2 факт. 4,2-5,0.    Заусенцы.    Несоответствующее формообразование левой торцевой поверхности, вид В.</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>Доработано подрядчиком</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" ht="22.95" customHeight="1">
+      <c r="A24" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>В00-0000064</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>13.05.2026</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000198 от 13.05.2026 13:53:20</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х454х470) зеркальная (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="9" t="n">
         <v>47.22</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>5±0,2 факт. 4,2-5,0.    Заусенцы.</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>Доработано подрядчиком</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" ht="22.95" customHeight="1">
+      <c r="A25" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>В00-0000065</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>14.05.2026</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001899 от 14.05.2026 10:55:15</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Строд Сервис (Самара) (ЭДО Такском ЗП 06.02.25)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>_уу_(ПРАВАЯ) Пленка для демпферного устройства ФО-2 фон+Сегмент 1(1шт)+Сегмент 1(2шт) (белая, черная</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>1.2.1.5 Световозвращающие пленки</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>Поставщик произвел замену пленки.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" ht="34.95" customHeight="1">
+      <c r="A26" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>В00-0000067</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>14.05.2026</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001898 от 14.05.2026 10:51:53</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>ОБЕСПЕЧЕНИЕ фирма ООО</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>_уу_Отвод 90-1-114,3х6,3 ГОСТ 17375-2001/Ст10</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>Детали трубопроводов 3D ГОСТ 17375-2001</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 17380 табл. 3 Размер 6,3-0,8 мм, фактически 5,0-5,6 мм.</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>Конструктором оформлено Разрешение на отступление от чертежа 01/КП 1760, КП 2274. Взять в работу в штатном режиме.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" ht="70.95" customHeight="1">
+      <c r="A27" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>В00-0000068</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>14.05.2026</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000201 от 14.05.2026 12:38:43</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Корпус №07</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="9" t="n">
         <v>16.24</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>Шаг несущей полосы 34 ± 1,5 мм, фактически 29 – 41 мм.    Р-р 746-2 фактически 742 – 746 мм (недостаток длины связующего элемента компенсирован наплавлением металла).    Сварка связующих элементов с крайними несущими полосами выполнена на прихватках.     Максимальное выступание связующих элементов над несущими полосами не более 1,5 мм, фактически 3 мм.    Дефекты сварных швов:    Несплавления связующих полос с несущими.    Брызги металла, наплывы.</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами работников УПН</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" ht="82.05" customHeight="1">
+      <c r="A28" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>В00-0000069</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>15.05.2026</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>М-СТАЛЬ ООО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>М-СТАЛЬ ООО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>(ПФ) Четверть вторая (четвертая) оболочки нижней секции (раскрой)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="9" t="n">
         <v>388.55</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>1.Геометрические размеры:    Размер 482±2 – факт. 478;    Размер 868±2 – факт. 864;    Паз 14+0,5х90+1 – факт 14,9х90;    Отверстие ф25+2 – факт. 24,5;    Пазы 5±1х5±1х5±1 – факт. 5х3х3.    2.Отклонения от плоскостности детали:    Условная вершина условного нижнего    основания трапеции – 9 мм;    Нижняя часть трапеции – 6 мм;    Центральная часть трапеции – 3 мм;    По условным граням (линии гиба) слева    направо – 7; 10; 7;5.    3.Дефекты термической резки:    Цепочки застывших капель, облой, шлак,    выхватывания.</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>Изготовление опытного образца</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" ht="82.05" customHeight="1">
+      <c r="A29" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>В00-0000070</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>19.05.2026</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000205 от 18.05.2026 15:11:01</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="8" t="n">
         <v>243.6</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>Р-р 746-2 фактически 743 – 746 мм (недостаток длины связующего элемента компенсирован наплавлением металла). Выступание связующих элементов по СТО не более 1,5мм, фактически до 4мм. Занижение обрамляющего элемента по СТО не более 1мм, фактически до 4мм. Выступание обрамляющего элемента по СТО не более 1мм, фактически до 4мм. Выгнутость по СТО не более 3мм, фактически до 5мм. Механические повреждения. Дефекты сварных швов: брызги металла, кратеры, поры, натёки, прожоги, несплавления.</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="Q29" s="7" t="n"/>
+    </row>
+    <row r="30" ht="34.95" customHeight="1">
+      <c r="A30" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>В00-0000071</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>20.05.2026</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002037 от 19.05.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>МЕТИЗКОМПЛЕКТ ПК ООО(ЭДО Такском ЗП согл. от 01.04.2026)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>БЕЗ МАРКИРОВКИ_ГПЦ(закупка) Болт М16-6azx60.58.0940 ГОСТ 7802-81 Оцинкованное</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>Метизы</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="12" t="n">
         <v>1900</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="8" t="n">
         <v>229.9</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>Отсутствует маркировка класса прочности. Диаметр головки по ГОСТ7802  35+-0.8мм, фактически 37,28-37,96мм. Высота головки по ГОСТ 7802 8+-0,45мм, фактически 10мм. Неполный профиль резьбы.</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>Письмо Снегирев</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" ht="22.95" customHeight="1">
+      <c r="A31" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>В00-0000071</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>20.05.2026</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002037 от 19.05.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>МЕТИЗКОМПЛЕКТ ПК ООО(ЭДО Такском ЗП согл. от 01.04.2026)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>ГПЦ(закупка) (в ШТ) Гайка М16-6H.6.0930 ГОСТ 5915-70 Оцинкованное</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>Метизы</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>Высота гайки по ГОСТ 5915 14,8-1,1мм, фактически 12,84-12,99мм.</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="7" t="inlineStr">
         <is>
           <t>Письмо Снегирев</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" ht="34.95" customHeight="1">
+      <c r="A32" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>В00-0000072</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>22.05.2026</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000221 от 21.05.2026 16:47:49</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="14" t="n">
         <v>6990.4</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>ЭЗ 248.00.00.000 СБ:    Не выполнено требование "Заварить"         Дефекты сварных швов:    брызги металла, подрезы, шлак, несплавление.        Дефекты лазерной резки: незавершенный рез, налипший шлак.</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" ht="22.95" customHeight="1">
+      <c r="A33" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>В00-0000073</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>22.05.2026</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000223 от 22.05.2026 13:04:19</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="14" t="n">
         <v>3495.2</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>ЭЗ 248.00.00.000 СБ:Не выполнено требование "Заварить". Дефекты сварных швов: брызги металла, подрезы, шлак, несплавление, остатки сварочной проволоки.</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" ht="22.95" customHeight="1">
+      <c r="A34" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>В00-0000074</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>23.05.2026</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000225 от 23.05.2026 8:39:12</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Опора МСО-ФГ-7-9-01 СТО 07525912-300-2021 (ФГС-700-9,0-01) (ОО 345.00.00.000 СБ)  (от п</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="10" t="n">
         <v>3890.25</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>Брызги металла. Несплавления. Остатки сварочной проволоки.</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="Q34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="58.95" customHeight="1">
+      <c r="A35" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>В00-0000075</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>23.05.2026</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000226 от 23.05.2026 12:44:03</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2380) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="10" t="n">
         <v>1546.95</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Малозначительное Неустранимое</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>Размер 2380+-2мм, фактически 2384мм (1шт). Размер кромки 100+1мм, фактически 199мм. Размер до тех. отверстия 35+-1мм, фактически 30мм (2шт). Размер между тех. отверстиями 770+-1мм, фактически 770мм, 685мм, 871мм (2шт). Размер кромки 15+-1мм, фактически 13-15мм Отсутствует кромка 20+-0,3*3+-1.Размер 55+-0,4мм, фактически 53,69-56,81мм. Заусенцы. Остатки силиконового герметика..</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами работников ОЭУ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" ht="46.95" customHeight="1">
+      <c r="A36" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>В00-0000076</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>25.05.2026</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000232 от 25.05.2026 8:18:56</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Опора МСО-ФГ-7-9-01 СТО 07525912-300-2021 (ФГС-700-9,0-01) (ОО 345.00.00.000 СБ)  (от п</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="L36" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="12" t="n">
         <v>1482</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P36" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: остатки сварочной проволоки, брызги металла, несплавления, кратеры, поры, неравномерная ширина шва, плохое повторное возбуждение дуги. Не выполнено требование "Заварить". Дефекты лазерной резки: налипший шлак, незавершённый рез .</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="Q36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="34.95" customHeight="1">
+      <c r="A37" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>В00-0000077</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002106 от 25.05.2026 13:23:44</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>ТД ЭЛЕКТРОТЕХМОНТАЖ АО (ЭТМ)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>_уу_Шкаф распределительный ЩВ1+ЩВ2 по М 038.00.00.000 ЭЗ</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="M37" s="13" t="n"/>
+      <c r="N37" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД.</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" s="7" t="inlineStr">
         <is>
           <t>Карточка разрешения № 46 от 28.05.2026. Прошу допустить в дальнейшее производство работ без доработок по карточке разрешения.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" ht="22.95" customHeight="1">
+      <c r="A38" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>В00-0000078</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000247 от 26.05.2026 16:46:13</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="14" t="n">
         <v>10485.6</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P38" s="7" t="inlineStr">
         <is>
           <t>Не выполнено требование "Заварить". По КД сварной шов №2 между деталью 2 (ребро) и деталью 3 (фланец) катет 8, фактически 6 (1шт). Брызги металла (1 шт).</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" ht="58.95" customHeight="1">
+      <c r="A39" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>В00-0000079</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000246 от 26.05.2026 14:39:35</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2380) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="9" t="n">
         <v>928.17</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>1.Размер 40±0,3 мм, фактически 38-40 мм.    2.Размер 100+1 мм, фактически 119-120 мм.    2. Размер 5±0,2 мм фактически 4,1-4,3 мм (на одной пластине).    3.Отсутствует кромка 20±0,3*3±1 мм.     4.Профиль фаски 15х25˚ не соответствует заданному на Ц 184.04.00.001 выносной элемент Б. Подрезание (местное углубление на обработанной поверхности) до 1 мм на длине 100 мм - 2380 мм.    5.Заусенцы.</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" s="7" t="inlineStr">
         <is>
           <t>КР №50 от 02.06.2026, Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" ht="58.95" customHeight="1">
+      <c r="A40" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>В00-0000079</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000246 от 26.05.2026 14:39:35</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2385) зеркальная (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="9" t="n">
         <v>310.04</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>1.Размер 40±0,3 мм, фактически 38-40 мм.    2.Размер 100+1 мм, фактически 119-120 мм.    3.Отсутствует кромка 20±0,3*3±1 мм.     4.Профиль фаски 15х250 не соответствует заданному на Ц 184.04.00.001 выносной элемент Б. Подрезание (местное углубление на обработанной поверхности) до 1 мм на длине 100 мм - 2385 мм.    5.Заусенцы.</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" s="7" t="inlineStr">
         <is>
           <t>КР №50 от 02.06.2026, Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" ht="70.95" customHeight="1">
+      <c r="A41" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>В00-0000079</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000246 от 26.05.2026 14:39:35</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2385) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="L41" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" s="9" t="n">
         <v>310.04</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P41" s="7" t="inlineStr">
         <is>
           <t>Фактически пластина 32х570х2380 мм.    1.Размер 40±0,3 мм, фактически 38-40 мм.    2.Размер 100+1 мм, фактически 119-120 мм.    3.Отсутствует кромка 20±0,3*3±1 мм.     4.Профиль фаски 15х250 не соответствует заданному на Ц 184.05.00.001-01 выносной элемент Б. Подрезание (местное углубление на обработанной поверхности) до 1 мм на длине 100 мм - 2380 мм.    5.Заусенцы.    6.Дефект плазменной резки – незавершенный рез.</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" s="7" t="inlineStr">
         <is>
           <t>КР №50 от 02.06.2026, Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" ht="22.95" customHeight="1">
+      <c r="A42" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>В00-0000080</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>_Склад корпус №8</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="L42" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42" s="14" t="n">
         <v>6990.4</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P42" s="7" t="inlineStr">
         <is>
           <t>ЭЗ 248.00.00.000 СБ: Не выполнено требование "Заварить".</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" ht="22.95" customHeight="1">
+      <c r="A43" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>В00-0000081</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000243 от 26.05.2026 10:31:31</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР8 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="L43" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" s="10" t="n">
         <v>4054.25</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P43" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
+      <c r="Q43" s="7" t="n"/>
+    </row>
+    <row r="44" ht="22.95" customHeight="1">
+      <c r="A44" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>В00-0000081</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>27.05.2026</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000243 от 26.05.2026 10:31:31</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР19 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="L44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44" s="10" t="n">
         <v>1024.26</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P44" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
+      <c r="Q44" s="7" t="n"/>
+    </row>
+    <row r="45" ht="70.95" customHeight="1">
+      <c r="A45" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>В00-0000082</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>28.05.2026</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000256 от 27.05.2026 18:42:52</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="L45" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45" s="10" t="n">
         <v>2338.56</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P45" s="7" t="inlineStr">
         <is>
           <t>По СТО выступание связующих элементов над несущими полосами не более 1,5мм, фактически до 3,4мм. По СТО занижение обрамляющего элемента относительно несущей полосы не более 1мм, фактически до 5мм. Р-р 746-2 фактически 742 – 746 мм (недостаток длины связующего элемента компенсирован наплавлением металла). Механические повреждения. Дефекты сварки: несплавления, натёки, поры, прожог (1шт), остатки сварочной проволоки (1шт).</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" s="7" t="inlineStr">
         <is>
           <t>КР 51 от 02.06.2026, несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" ht="22.95" customHeight="1">
+      <c r="A46" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>В00-0000083</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>30.05.2026</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000260 от 28.05.2026 14:43:31</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="L46" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M46" s="8" t="n">
         <v>873.8</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P46" s="7" t="inlineStr">
         <is>
           <t>1. Подрезы. 2. Брызги металла. 3. Незавареный кратер. 4. Не выполнено требование "Заварить".</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" ht="34.95" customHeight="1">
+      <c r="A47" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>В00-0000084</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>01.06.2026</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>_Склад корпус №11</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2380) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="L47" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47" s="10" t="n">
         <v>1546.95</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>Размер 2380+-2мм, фактически 2384мм (1шт). Отсутствует кромка 20+-0,3*3+-1.Размер 55+-0,4мм, фактически 53,69-56,81мм. Заусенцы. Остатки силиконового герметика..</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q47" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" ht="34.95" customHeight="1">
+      <c r="A48" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>В00-0000085</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000285 от 02.06.2026 9:21:20</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="L48" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M48" s="14" t="n">
         <v>3058.3</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N48" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P48" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 14771: ширина сварного шва С17 12+-2мм, фактически 6,4-15,4мм, высота сварного шва С17 1+-1мм, фактически до -0,77мм. Подрез (1шт). Натеки металла сварного шва У4 (1шт).</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q48" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" ht="22.95" customHeight="1">
+      <c r="A49" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>В00-0000086</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001983 от 14.05.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>МЕТАЛЛСЕРВИС-МОСКВА ООО</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Корпус №13</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>_уу_Полоса 5,0*30*6000 ГОСТ 103-2006/ Ст3сп</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>Листы сталь Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="L49" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49" s="11" t="n">
         <v>417.012</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P49" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 103 длина 6000+50 мм, фактически 875-6000 мм. Имеются дефекты ввиде перегиба (загиба, залома).</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
+      <c r="Q49" s="7" t="n"/>
+    </row>
+    <row r="50" ht="70.95" customHeight="1">
+      <c r="A50" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>В00-0000087</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000269 от 30.05.2026 16:35:59</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="L50" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M50" s="8" t="n">
         <v>243.6</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N50" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P50" s="7" t="inlineStr">
         <is>
           <t>Выступание связующих элементов по СТО не более 1,5мм, фактически до 5мм. Занижение обрамляющего элемента по СТО не более 1мм, фактически до 5мм. Выступание обрамляющего элемента по СТО не более 1мм, фактически до 3мм. Выгнутость по СТО не более 8мм, фактически до 11мм. Механические повреждения. Дефекты сварных швов: брызги металла, кратеры, поры, натёки, прожоги, несплавления.</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
+      <c r="Q50" s="7" t="n"/>
+    </row>
+    <row r="51" ht="58.95" customHeight="1">
+      <c r="A51" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>В00-0000088</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="L51" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M51" s="8" t="n">
         <v>731.2</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P51" s="7" t="inlineStr">
         <is>
           <t>1.На локальных участках дефекты сварных швов: брызги металла, плохое повторное возбуждение дуги. Доработано в процессе контроля сотрудником ОА «Завод Продмаш».    2.Разнооттеночность очищенной поверхности от светло-серого до темно-серого цвета, на торцевых поверхностях деталей и отверстий «бурая ржавчина».     Шероховатость поверхности Rz от 30 до 80 мкм.</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" ht="46.95" customHeight="1">
+      <c r="A52" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>В00-0000089</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>03.06.2026</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L52" t="n">
+      <c r="L52" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M52" s="10" t="n">
         <v>1608.64</v>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P52" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов:    Поры, плохое повторное возбуждение дуги, отсутствие плавного перехода к основному металлу. Устранено в процессе контроля.     Состояние поверхности:    "бурая ржавчина" на локальных участках.     На двух изделиях шероховатость от 9 до 54 мкм (ср. 33 мкм), от 7 до 54 мкм (ср. 29 мкм)</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q52" s="7" t="inlineStr">
         <is>
           <t>Проведен контроль после повторной дробеструйной обработки, несоответствия не выявлены</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" ht="46.95" customHeight="1">
+      <c r="A53" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>В00-0000090</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>09.06.2026</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="I53" s="7" t="n"/>
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L53" t="n">
+      <c r="L53" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53" s="14" t="n">
         <v>1462.4</v>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P53" s="7" t="inlineStr">
         <is>
           <t>После нанесения финишного слоя. Класс покрытия V, средняя толщина 350 – 399 мкм, 90/10 – выполнено.    Локальные участки с толщинами менее 265 мкм доработаны в процессе контроля.    На двух изделиях повреждения финишного слоя до грунта.</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" ht="22.95" customHeight="1">
+      <c r="A54" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>В00-0000090</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>09.06.2026</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="I54" s="7" t="n"/>
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="L54" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M54" s="9" t="n">
         <v>877.4400000000001</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N54" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P54" s="7" t="inlineStr">
         <is>
           <t>После нанесения второго слоя грунта. Класс покрытия V, средняя толщина 360 – 410 мкм, 90/10 – выполнено.</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
+      <c r="Q54" s="7" t="n"/>
+    </row>
+    <row r="55" ht="22.95" customHeight="1">
+      <c r="A55" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>В00-0000091</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="16" t="inlineStr">
         <is>
           <t>10.06.2026</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000330 от 09.06.2026 15:09:30</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-24/4/К230-2,5 (ЭЗ 249.00.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="L55" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M55" s="9" t="n">
         <v>457.65</v>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N55" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок/ скругление</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P55" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q55" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены УМИ</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" ht="22.95" customHeight="1">
+      <c r="A56" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>В00-0000092</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>10.06.2026</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000328 от 09.06.2026 10:13:01</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-24/4/К230-2,5 (ЭЗ 249.00.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="L56" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M56" s="9" t="n">
         <v>457.65</v>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок/ скругление</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P56" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены УМИ</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" ht="22.95" customHeight="1">
+      <c r="A57" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>В00-0000093</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>10.06.2026</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002480 от 08.06.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>МЕТАЛЛОТОРГ АО (ЭДО Такском ПМ, ЗП+)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="7" t="inlineStr">
         <is>
           <t>_уу_Труба 15*2,8 ГОСТ 3262-75/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>2.1.1.2.1.8 Трубы стальные водогазопроводные ГОСТ 3262-75</t>
         </is>
       </c>
-      <c r="L57" t="n">
+      <c r="L57" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M57" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N57" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P57" s="7" t="inlineStr">
         <is>
           <t>Содержание кремния 0,02-0,04% (ГОСТ 380 сталь Ст3сп содержание кремния 0,15-0,30%).</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
+      <c r="Q57" s="7" t="n"/>
+    </row>
+    <row r="58" ht="22.95" customHeight="1">
+      <c r="A58" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>В00-0000094</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="22" t="n"/>
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>11.06.2026</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000342 от 11.06.2026 9:31:44</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х11,1/30х3 А 715х1380 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L58" t="n">
+      <c r="L58" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M58" s="14" t="n">
         <v>1576.2</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>Разность диагоналей настила</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P58" s="7" t="inlineStr">
         <is>
           <t>Разность диагоналей настила фактически 15-17 мм (по СТО 07525912-050-2024 табл. В.1 не более 0,01*1380=13,8 мм)</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q58" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" ht="34.95" customHeight="1">
+      <c r="A59" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>В00-0000095</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="22" t="n"/>
+      <c r="E59" s="16" t="inlineStr">
         <is>
           <t>16.06.2026</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000353 от 16.06.2026 8:39:56</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-24/4/К230-2,5 (ЭЗ 249.00.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L59" t="n">
+      <c r="L59" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M59" s="9" t="n">
         <v>183.06</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N59" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P59" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: 1. Брызги металла. 2. Поры. Дефекты термической резки: 1. Неполный рез. 2. Налипший шлак.  Несоответствия требованиям КД: 1. Не выполнено притуплние кромок дет.3.</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q59" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" ht="22.95" customHeight="1">
+      <c r="A60" s="3" t="n">
         <v>163</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t>В00-0000096</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="16" t="inlineStr">
         <is>
           <t>16.06.2026</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000357 от 16.06.2026 13:20:28</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Кронштейн 1.К2-2,0-1,5-0/180-Ф4 (МС 866.00.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L60" t="n">
+      <c r="L60" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M60" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N60" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P60" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: Подрез. Несоответствия требованиям КД: Отсутствуют  технологические отверстия на детали 3</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+      <c r="Q60" s="7" t="n"/>
+    </row>
+    <row r="61" ht="22.95" customHeight="1">
+      <c r="A61" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>В00-0000097</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="16" t="inlineStr">
         <is>
           <t>18.06.2026</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000364 от 18.06.2026 13:50:28</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L61" t="n">
+      <c r="L61" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M61" s="10" t="n">
         <v>1092.25</v>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N61" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок/ скругление</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P61" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок детал поз.4</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q61" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены УМИ</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" ht="22.95" customHeight="1">
+      <c r="A62" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>В00-0000098</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="22" t="n"/>
+      <c r="E62" s="16" t="inlineStr">
         <is>
           <t>17.06.2026</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП11 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="L62" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62" s="10" t="n">
         <v>3601.75</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N62" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P62" s="7" t="inlineStr">
         <is>
           <t>Плохое повторное ывозобнавление дуги, брызги металла, пора.</t>
         </is>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
+      <c r="Q62" s="7" t="n"/>
+    </row>
+    <row r="63" ht="22.95" customHeight="1">
+      <c r="A63" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>В00-0000099</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="16" t="inlineStr">
         <is>
           <t>18.06.2026</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002670 от 18.06.2026 14:45:21</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>СамараПромснаб ПК</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="7" t="inlineStr">
         <is>
           <t>(ОО_ПФ) Втулка МФГ-М 001.20.20.002 (резка в размер), (опытный образец)</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" s="7" t="inlineStr">
         <is>
           <t>Проект ЗАВЕРШЕН "Модернизация конструктива короны и оголовка" 1-000000083 Ушков А.В.</t>
         </is>
       </c>
-      <c r="L63" t="n">
+      <c r="L63" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N63" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P63" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 10704 п.4: +-0,3 мм, факт 12,42 мм; п.6: +-10%, факт от 1,06 мм до 1,73 мм</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
+      <c r="Q63" s="7" t="n"/>
+    </row>
+    <row r="64" ht="22.95" customHeight="1">
+      <c r="A64" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>В00-0000100</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="22" t="n"/>
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>23.06.2026</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000372 от 22.06.2026 8:35:40</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K64" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L64" t="n">
+      <c r="L64" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M64" s="10" t="n">
         <v>1966.05</v>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>Несоответствие геометрических размеров</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P64" s="7" t="inlineStr">
         <is>
           <t>Деталь №4: Труба 219*8мм, фактически сварена из труб 219*8 и 219*6</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
+      <c r="Q64" s="7" t="n"/>
+    </row>
+    <row r="65" ht="22.95" customHeight="1">
+      <c r="A65" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>В00-0000101</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="16" t="inlineStr">
         <is>
           <t>23.06.2026</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000375 от 23.06.2026 8:35:44</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K65" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L65" t="n">
+      <c r="L65" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M65" s="9" t="n">
         <v>218.45</v>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N65" s="7" t="inlineStr">
         <is>
           <t>Несоответствие геометрических размеров</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P65" s="7" t="inlineStr">
         <is>
           <t>Деталь №4: Труба 219*8мм, фактически сварена из труб 219*8 и 219*6</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
+      <c r="Q65" s="7" t="n"/>
+    </row>
+    <row r="66" ht="22.95" customHeight="1">
+      <c r="A66" s="3" t="n">
         <v>169</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>В00-0000103</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000389 от 26.06.2026 9:24:35</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С2 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L66" t="n">
+      <c r="L66" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M66" s="9" t="n">
         <v>193.23</v>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="N66" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P66" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, плохое повторное возобновление дуги, не заваренный кратер, пора</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
+      <c r="Q66" s="7" t="n"/>
+    </row>
+    <row r="67" ht="22.95" customHeight="1">
+      <c r="A67" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>В00-0000103</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="22" t="n"/>
+      <c r="E67" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000389 от 26.06.2026 9:24:35</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С2.1 (пром.) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L67" t="n">
+      <c r="L67" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M67" t="n">
+      <c r="M67" s="9" t="n">
         <v>46.05</v>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>Плохое повторное возбуждение дуги</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P67" s="7" t="inlineStr">
         <is>
           <t>Плохое повторное возбуждение дуги</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
+      <c r="Q67" s="7" t="n"/>
+    </row>
+    <row r="68" ht="22.95" customHeight="1">
+      <c r="A68" s="3" t="n">
         <v>171</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>В00-0000103</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="C68" s="21" t="n"/>
+      <c r="D68" s="22" t="n"/>
+      <c r="E68" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000389 от 26.06.2026 9:24:35</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С2.1 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K68" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L68" t="n">
+      <c r="L68" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="M68" t="n">
+      <c r="M68" s="8" t="n">
         <v>404.1</v>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N68" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P68" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, плохое повторное возобновление дуги, пора, натек. Не выполнено требование КД "заварить".</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
+      <c r="Q68" s="7" t="n"/>
+    </row>
+    <row r="69" ht="22.95" customHeight="1">
+      <c r="A69" s="3" t="n">
         <v>172</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>В00-0000103</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="22" t="n"/>
+      <c r="E69" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000389 от 26.06.2026 9:24:35</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С3.1 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K69" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L69" t="n">
+      <c r="L69" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M69" s="9" t="n">
         <v>39.49</v>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="N69" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P69" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
+      <c r="Q69" s="7" t="n"/>
+    </row>
+    <row r="70" ht="22.95" customHeight="1">
+      <c r="A70" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>В00-0000104</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="C70" s="21" t="n"/>
+      <c r="D70" s="22" t="n"/>
+      <c r="E70" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000394 от 26.06.2026 16:45:41</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С1 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L70" t="n">
+      <c r="L70" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M70" s="9" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr">
         <is>
           <t>Единичные поры</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P70" s="7" t="inlineStr">
         <is>
           <t>Единичная пора</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
+      <c r="Q70" s="7" t="n"/>
+    </row>
+    <row r="71" ht="22.95" customHeight="1">
+      <c r="A71" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>В00-0000104</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="C71" s="21" t="n"/>
+      <c r="D71" s="22" t="n"/>
+      <c r="E71" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000394 от 26.06.2026 16:45:41</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С1.1 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K71" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L71" t="n">
+      <c r="L71" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M71" t="n">
+      <c r="M71" s="8" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="N71" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P71" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, пора, незаваренный кратер</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
+      <c r="Q71" s="7" t="n"/>
+    </row>
+    <row r="72" ht="22.95" customHeight="1">
+      <c r="A72" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>В00-0000104</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="22" t="n"/>
+      <c r="E72" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000394 от 26.06.2026 16:45:41</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С3 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L72" t="n">
+      <c r="L72" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M72" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N72" s="7" t="inlineStr">
         <is>
           <t>Натек</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P72" s="7" t="inlineStr">
         <is>
           <t>Натек металла</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
+      <c r="Q72" s="7" t="n"/>
+    </row>
+    <row r="73" ht="22.95" customHeight="1">
+      <c r="A73" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>В00-0000105</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="C73" s="21" t="n"/>
+      <c r="D73" s="22" t="n"/>
+      <c r="E73" s="16" t="inlineStr">
         <is>
           <t>30.06.2026</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002805 от 24.06.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>ТД ЭЛЕКТРОТЕХМОНТАЖ АО (ЭТМ)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="7" t="inlineStr">
         <is>
           <t>_уу_Шкаф распределительный ЩВ1 + 3 КЗНС МФГ25-М(500)-IV-3-цл (23М)</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K73" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L73" t="n">
+      <c r="L73" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="M73" s="13" t="n"/>
+      <c r="N73" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P73" s="7" t="inlineStr">
         <is>
           <t>Акт во вложении.</t>
         </is>
       </c>
+      <c r="Q73" s="7" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q73">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="73">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>